--- a/data/analysis_gemini_3_6_flash_panns/multimodal_event_eval_gemini_3_6_flash_panns_w2_5s_h1_25s.xlsx
+++ b/data/analysis_gemini_3_6_flash_panns/multimodal_event_eval_gemini_3_6_flash_panns_w2_5s_h1_25s.xlsx
@@ -115,16 +115,16 @@
     <t>gunshot_or_explosion(24-240)</t>
   </si>
   <si>
-    <t>sound: speech(0-120), sound: burst_pop(90-150), sound: gunshot_or_explosion(120-180), sound: engine(150-240), visual: explosion_visible(120-240), visual: gunshot_visible(24-96), visual: physical_altercation(48-96), visual: running(144-240), visual: running(120-240), visual: suspicious_near_vehicle(24-48), visual: suspicious_near_vehicle(120-120)</t>
-  </si>
-  <si>
-    <t>gunshot_or_explosion(60-120)</t>
+    <t>sound: gunshot_or_explosion(90-180), sound: engine(150-240), visual: explosion_visible(120-240), visual: gunshot_visible(24-96), visual: physical_altercation(48-96), visual: running(144-240), visual: running(120-240), visual: suspicious_near_vehicle(24-48), visual: suspicious_near_vehicle(120-120)</t>
+  </si>
+  <si>
+    <t>gunshot_or_explosion(30-120)</t>
   </si>
   <si>
     <t>gunshot_or_explosion(120-180)</t>
   </si>
   <si>
-    <t>sound: engine(0-60), sound: engine(150-240), sound: speech(30-150), sound: gunshot_or_explosion(120-180), visual: gunshot_visible(120-120), visual: physical_altercation(96-96), visual: running(144-144), visual: running(120-120), visual: suspicious_near_vehicle(48-96), visual: suspicious_near_vehicle(216-240), visual: suspicious_near_vehicle(72-72), visual: suspicious_near_vehicle(216-240), visual: suspicious_near_vehicle(24-96), visual: suspicious_near_vehicle(168-192), visual: suspicious_near_vehicle(96-96)</t>
+    <t>sound: engine(0-60), sound: engine(150-240), sound: gunshot_or_explosion(120-180), visual: gunshot_visible(120-120), visual: physical_altercation(96-96), visual: running(144-144), visual: running(120-120), visual: suspicious_near_vehicle(48-96), visual: suspicious_near_vehicle(216-240), visual: suspicious_near_vehicle(72-72), visual: suspicious_near_vehicle(216-240), visual: suspicious_near_vehicle(24-96), visual: suspicious_near_vehicle(168-192), visual: suspicious_near_vehicle(96-96)</t>
   </si>
   <si>
     <t>gunshot_or_explosion(0-240)</t>
@@ -133,31 +133,31 @@
     <t>NO</t>
   </si>
   <si>
-    <t>sound: door(0-90), sound: engine(60-240), visual: enter_or_exit_vehicle(48-120), visual: suspicious_near_vehicle(24-72)</t>
+    <t>sound: engine(60-240), visual: enter_or_exit_vehicle(48-120), visual: suspicious_near_vehicle(24-72)</t>
   </si>
   <si>
     <t>vehicle_escape(24-216)</t>
   </si>
   <si>
-    <t>sound: animal(0-60), sound: door(30-90), sound: engine(60-240), visual: enter_or_exit_vehicle(48-96), visual: suspicious_near_vehicle(24-216)</t>
+    <t>sound: engine(60-240), visual: enter_or_exit_vehicle(48-96), visual: suspicious_near_vehicle(24-216)</t>
   </si>
   <si>
     <t>vehicle_collision(96-216)</t>
   </si>
   <si>
-    <t>sound: horn(0-90), sound: breaking(60-150), sound: engine(120-210), sound: door(180-240), visual: enter_or_exit_vehicle(120-192), visual: running(48-96), visual: suspicious_near_vehicle(120-168), visual: vehicle_collision(120-216), visual: vehicle_collision(96-96)</t>
+    <t>sound: horn(0-90), sound: engine(120-210), visual: enter_or_exit_vehicle(120-192), visual: running(48-96), visual: suspicious_near_vehicle(120-168), visual: vehicle_collision(120-216), visual: vehicle_collision(96-96)</t>
   </si>
   <si>
     <t>vehicle_collision(30-240)</t>
   </si>
   <si>
-    <t>sound: engine(0-60), sound: skidding(30-90), sound: gunshot_or_explosion(60-120), sound: glass_breaking(90-150), sound: speech(120-240), visual: carrying(0-240), visual: vehicle_collision(72-240)</t>
+    <t>sound: engine(0-60), sound: skidding(30-90), sound: gunshot_or_explosion(60-120), sound: glass_breaking(90-150), visual: carrying(0-240), visual: vehicle_collision(72-240)</t>
   </si>
   <si>
     <t>vehicle_collision(72-240)</t>
   </si>
   <si>
-    <t>sound: horn(0-60), sound: engine(30-240), sound: gunshot_or_explosion(60-120), sound: breaking(90-150), visual: enter_or_exit_vehicle(144-168), visual: suspicious_near_vehicle(144-240), visual: vehicle_collision(72-72), visual: vehicle_collision(72-240)</t>
+    <t>sound: horn(0-60), sound: engine(30-240), sound: gunshot_or_explosion(60-120), visual: enter_or_exit_vehicle(144-168), visual: suspicious_near_vehicle(144-240), visual: vehicle_collision(72-72), visual: vehicle_collision(72-240)</t>
   </si>
   <si>
     <t>loitering(24-216)</t>

--- a/data/analysis_gemini_3_6_flash_panns/multimodal_event_eval_gemini_3_6_flash_panns_w2_5s_h1_25s.xlsx
+++ b/data/analysis_gemini_3_6_flash_panns/multimodal_event_eval_gemini_3_6_flash_panns_w2_5s_h1_25s.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="51">
   <si>
     <t>event</t>
   </si>
@@ -103,31 +103,28 @@
     <t>YES</t>
   </si>
   <si>
-    <t>fight(0-192)</t>
-  </si>
-  <si>
-    <t>fight(24-168)</t>
-  </si>
-  <si>
-    <t>fight(48-48)</t>
-  </si>
-  <si>
-    <t>gunshot_or_explosion(24-240)</t>
+    <t>sound: engine(150-210), visual: physical_altercation(0-168), visual: physical_altercation(120-120), visual: physical_altercation(192-192), visual: physical_altercation(144-168), visual: running(48-72)</t>
+  </si>
+  <si>
+    <t>visual: physical_altercation(24-96), visual: physical_altercation(120-144), visual: physical_altercation(168-168), visual: running(192-192), visual: running(96-96), visual: running(192-192)</t>
+  </si>
+  <si>
+    <t>sound: engine(180-240), visual: physical_altercation(48-48)</t>
   </si>
   <si>
     <t>sound: gunshot_or_explosion(90-180), sound: engine(150-240), visual: explosion_visible(120-240), visual: gunshot_visible(24-96), visual: physical_altercation(48-96), visual: running(144-240), visual: running(120-240), visual: suspicious_near_vehicle(24-48), visual: suspicious_near_vehicle(120-120)</t>
   </si>
   <si>
-    <t>gunshot_or_explosion(30-120)</t>
-  </si>
-  <si>
-    <t>gunshot_or_explosion(120-180)</t>
+    <t>sound: engine(0-60), sound: gunshot_or_explosion(30-120), visual: running(96-120), visual: running(96-96), visual: running(192-192), visual: suspicious_near_vehicle(48-48), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(48-48)</t>
   </si>
   <si>
     <t>sound: engine(0-60), sound: engine(150-240), sound: gunshot_or_explosion(120-180), visual: gunshot_visible(120-120), visual: physical_altercation(96-96), visual: running(144-144), visual: running(120-120), visual: suspicious_near_vehicle(48-96), visual: suspicious_near_vehicle(216-240), visual: suspicious_near_vehicle(72-72), visual: suspicious_near_vehicle(216-240), visual: suspicious_near_vehicle(24-96), visual: suspicious_near_vehicle(168-192), visual: suspicious_near_vehicle(96-96)</t>
   </si>
   <si>
-    <t>gunshot_or_explosion(0-240)</t>
+    <t>sound: gunshot_or_explosion(0-90), sound: engine(60-120), sound: engine(180-240), visual: explosion_visible(24-240), visual: running(24-48), visual: running(168-192), visual: running(72-144)</t>
+  </si>
+  <si>
+    <t>sound: gunshot_or_explosion(0-90), sound: engine(120-240), visual: explosion_visible(48-240), visual: running(144-168), visual: running(96-96), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(24-120), visual: suspicious_near_vehicle(240-240)</t>
   </si>
   <si>
     <t>NO</t>
@@ -136,70 +133,70 @@
     <t>sound: engine(60-240), visual: enter_or_exit_vehicle(48-120), visual: suspicious_near_vehicle(24-72)</t>
   </si>
   <si>
-    <t>vehicle_escape(24-216)</t>
+    <t>sound: engine(60-240), visual: enter_or_exit_vehicle(72-216), visual: running(24-24), visual: suspicious_near_vehicle(48-48)</t>
   </si>
   <si>
     <t>sound: engine(60-240), visual: enter_or_exit_vehicle(48-96), visual: suspicious_near_vehicle(24-216)</t>
   </si>
   <si>
-    <t>vehicle_collision(96-216)</t>
+    <t>visual: enter_or_exit_vehicle(48-96), visual: suspicious_near_vehicle(24-216)</t>
   </si>
   <si>
     <t>sound: horn(0-90), sound: engine(120-210), visual: enter_or_exit_vehicle(120-192), visual: running(48-96), visual: suspicious_near_vehicle(120-168), visual: vehicle_collision(120-216), visual: vehicle_collision(96-96)</t>
   </si>
   <si>
-    <t>vehicle_collision(30-240)</t>
-  </si>
-  <si>
     <t>sound: engine(0-60), sound: skidding(30-90), sound: gunshot_or_explosion(60-120), sound: glass_breaking(90-150), visual: carrying(0-240), visual: vehicle_collision(72-240)</t>
   </si>
   <si>
-    <t>vehicle_collision(72-240)</t>
-  </si>
-  <si>
     <t>sound: horn(0-60), sound: engine(30-240), sound: gunshot_or_explosion(60-120), visual: enter_or_exit_vehicle(144-168), visual: suspicious_near_vehicle(144-240), visual: vehicle_collision(72-72), visual: vehicle_collision(72-240)</t>
   </si>
   <si>
-    <t>loitering(24-216)</t>
-  </si>
-  <si>
-    <t>loitering(24-240)</t>
+    <t>visual: enter_or_exit_vehicle(144-168), visual: running(192-192), visual: suspicious_near_vehicle(24-216)</t>
+  </si>
+  <si>
+    <t>visual: suspicious_near_vehicle(24-240)</t>
   </si>
   <si>
     <t>visual: enter_or_exit_vehicle(144-168), visual: running(120-120), visual: suspicious_near_vehicle(24-216)</t>
   </si>
   <si>
-    <t>handoff(0-192), handoff(0-192)</t>
-  </si>
-  <si>
-    <t>handoff(24-216), handoff(24-216)</t>
-  </si>
-  <si>
-    <t>handoff(48-120), handoff(48-168), handoff(48-120), handoff(72-168), handoff(48-168), handoff(72-168)</t>
-  </si>
-  <si>
-    <t>fight(48-144)</t>
-  </si>
-  <si>
-    <t>fight(24-120)</t>
-  </si>
-  <si>
-    <t>vehicle_escape(0-168)</t>
-  </si>
-  <si>
-    <t>vehicle_collision(48-240)</t>
-  </si>
-  <si>
-    <t>loitering(24-192)</t>
+    <t>visual: carrying(0-96), visual: carrying(120-192)</t>
+  </si>
+  <si>
+    <t>visual: carrying(120-216), visual: carrying(120-120), visual: carrying(24-96)</t>
+  </si>
+  <si>
+    <t>visual: carrying(48-48), visual: carrying(48-48), visual: carrying(72-120), visual: carrying(120-120), visual: carrying(144-168), visual: running(72-96), visual: running(168-168)</t>
+  </si>
+  <si>
+    <t>visual: physical_altercation(48-144)</t>
+  </si>
+  <si>
+    <t>visual: physical_altercation(24-120), visual: running(24-24), visual: running(192-192), visual: running(192-192)</t>
+  </si>
+  <si>
+    <t>sound: engine(90-240), visual: enter_or_exit_vehicle(48-168), visual: running(0-48), visual: suspicious_near_vehicle(48-168)</t>
+  </si>
+  <si>
+    <t>sound: engine(60-240), visual: enter_or_exit_vehicle(48-168), visual: running(0-24), visual: suspicious_near_vehicle(48-144)</t>
+  </si>
+  <si>
+    <t>sound: horn(0-90), sound: engine(120-210), visual: enter_or_exit_vehicle(168-240), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(216-240), visual: vehicle_collision(72-240), visual: vehicle_collision(72-240)</t>
+  </si>
+  <si>
+    <t>sound: skidding(0-90), visual: suspicious_near_vehicle(216-240), visual: vehicle_collision(48-240), visual: vehicle_collision(48-240)</t>
+  </si>
+  <si>
+    <t>visual: enter_or_exit_vehicle(72-168), visual: running(216-240), visual: suspicious_near_vehicle(24-192)</t>
   </si>
   <si>
     <t>visual: enter_or_exit_vehicle(72-168), visual: running(48-48), visual: running(192-216), visual: suspicious_near_vehicle(48-168)</t>
   </si>
   <si>
-    <t>handoff(96-240), handoff(96-240)</t>
-  </si>
-  <si>
-    <t>handoff(24-240), handoff(24-240)</t>
+    <t>visual: carrying(120-240), visual: carrying(120-120), visual: carrying(96-96), visual: running(216-216), visual: running(144-144)</t>
+  </si>
+  <si>
+    <t>visual: carrying(24-120), visual: carrying(144-240), visual: carrying(120-120), visual: running(192-192)</t>
   </si>
 </sst>
 </file>
@@ -777,101 +774,101 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>28</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
       <c r="D2" t="s">
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
         <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -949,51 +946,51 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1010,7 +1007,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1054,7 +1051,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1071,139 +1068,139 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>18</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>20</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1220,6 +1217,182 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1228,7 +1401,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1252,10 +1425,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -1272,7 +1445,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1296,7 +1469,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -1308,15 +1481,15 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1340,27 +1513,27 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1384,27 +1557,27 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1428,27 +1601,27 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>29</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1472,27 +1645,27 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1516,239 +1689,63 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>31</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>32</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>36</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>34</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>35</v>
-      </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
       </c>
       <c r="E2" t="s">
         <v>48</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>36</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1765,6 +1762,94 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>37</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1773,7 +1858,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1797,51 +1882,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -1854,50 +1895,6 @@
       </c>
       <c r="E2" t="s">
         <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>38</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -2002,6 +1999,50 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2010,35 +2051,35 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>9</v>
       </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
       <c r="C2" t="s">
         <v>18</v>
       </c>
@@ -2047,50 +2088,6 @@
       </c>
       <c r="E2" t="s">
         <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2107,98 +2104,98 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/data/analysis_gemini_3_6_flash_panns/multimodal_event_eval_gemini_3_6_flash_panns_w2_5s_h1_25s.xlsx
+++ b/data/analysis_gemini_3_6_flash_panns/multimodal_event_eval_gemini_3_6_flash_panns_w2_5s_h1_25s.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="51">
   <si>
     <t>event</t>
   </si>
@@ -718,22 +718,22 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="D7">
-        <v>0.545</v>
+        <v>0.333</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H7">
         <v>5</v>
@@ -818,10 +818,10 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
       </c>
       <c r="E2" t="s">
         <v>29</v>
@@ -895,6 +895,50 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -917,7 +961,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -929,15 +973,15 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -946,15 +990,15 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -978,7 +1022,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -990,12 +1034,12 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
@@ -1007,40 +1051,524 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>33</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>17</v>
-      </c>
       <c r="B2" t="s">
         <v>12</v>
       </c>
@@ -1051,56 +1579,83 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>18</v>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>35</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -1112,656 +1667,50 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>19</v>
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>36</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>20</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>22</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>29</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>31</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>32</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>34</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>36</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
         <v>27</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>36</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
         <v>48</v>
       </c>
     </row>

--- a/data/analysis_gemini_3_6_flash_panns/multimodal_event_eval_gemini_3_6_flash_panns_w2_5s_h1_25s.xlsx
+++ b/data/analysis_gemini_3_6_flash_panns/multimodal_event_eval_gemini_3_6_flash_panns_w2_5s_h1_25s.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="52">
   <si>
     <t>event</t>
   </si>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>sound: engine(90-240), visual: enter_or_exit_vehicle(48-168), visual: running(0-48), visual: suspicious_near_vehicle(48-168)</t>
+  </si>
+  <si>
+    <t>visual: enter_or_exit_vehicle(48-168), visual: running(0-48), visual: suspicious_near_vehicle(48-168)</t>
   </si>
   <si>
     <t>sound: engine(60-240), visual: enter_or_exit_vehicle(48-168), visual: running(0-24), visual: suspicious_near_vehicle(48-144)</t>
@@ -666,22 +669,22 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0.8</v>
+        <v>0.714</v>
       </c>
       <c r="C5">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -1457,7 +1460,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1494,6 +1497,23 @@
         <v>43</v>
       </c>
     </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1535,7 +1555,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1579,7 +1599,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1623,7 +1643,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1667,7 +1687,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1705,13 +1725,13 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>48</v>
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1799,7 +1819,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1843,7 +1863,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
